--- a/research/6995.T/Reports/6995.T_DCF_Model.xlsx
+++ b/research/6995.T/Reports/6995.T_DCF_Model.xlsx
@@ -2502,9 +2502,10 @@
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8">
-        <f> Owner FCF</f>
-        <v>0</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>= Owner FCF</t>
+        </is>
       </c>
       <c r="B8" s="5">
         <v>10408</v>
